--- a/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Prod.xlsx
+++ b/KatalonData/EmailTextToPay/ManualEntry_CANAmount_Prod.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="94">
   <si>
     <t>Result</t>
   </si>
@@ -274,6 +274,51 @@
   </si>
   <si>
     <t>Wed Jun 03 17:17:43 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:41:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:42:39 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:43:29 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:44:21 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:45:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:46:09 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:46:56 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:47:40 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:48:22 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:49:08 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:49:51 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:50:42 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:51:27 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:52:12 IST 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 11:52:59 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -782,7 +827,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F033DD18-DD0F-43E3-A2D0-6223D1731E2C}">
-  <dimension ref="A1:AE7"/>
+  <dimension ref="A1:AD7"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="1" width="6.7265625" collapsed="true"/>
@@ -901,10 +946,10 @@
       </c>
     </row>
     <row ht="37.5" r="2" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" t="s" s="1">
         <v>64</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -937,11 +982,11 @@
       <c r="O2" s="18"/>
     </row>
     <row ht="37.5" r="3" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="B3" t="s">
-        <v>65</v>
+      <c r="B3" t="s" s="1">
+        <v>79</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>33</v>
@@ -976,11 +1021,11 @@
       <c r="O3" s="18"/>
     </row>
     <row ht="62.5" r="4" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="B4" t="s">
-        <v>66</v>
+      <c r="B4" t="s" s="1">
+        <v>80</v>
       </c>
       <c r="C4" s="16" t="s">
         <v>44</v>
@@ -1017,11 +1062,11 @@
       </c>
     </row>
     <row ht="62.5" r="5" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="B5" t="s">
-        <v>67</v>
+      <c r="B5" t="s" s="1">
+        <v>81</v>
       </c>
       <c r="C5" s="16" t="s">
         <v>45</v>
@@ -1058,11 +1103,11 @@
       </c>
     </row>
     <row ht="37.5" r="6" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="B6" t="s">
-        <v>68</v>
+      <c r="B6" t="s" s="1">
+        <v>82</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>49</v>
@@ -1123,11 +1168,11 @@
       </c>
     </row>
     <row ht="37.5" r="7" spans="1:30" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>47</v>
       </c>
-      <c r="B7" t="s">
-        <v>69</v>
+      <c r="B7" t="s" s="1">
+        <v>83</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>50</v>
@@ -1203,7 +1248,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35650B67-EEEE-43A0-9B0F-50672085E657}">
-  <dimension ref="A1:AF6"/>
+  <dimension ref="A1:AE6"/>
   <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" customWidth="true" style="5" width="7.26953125" collapsed="true"/>
@@ -1335,11 +1380,11 @@
       </c>
     </row>
     <row ht="37.5" r="2" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="5">
         <v>47</v>
       </c>
-      <c r="B2" t="s">
-        <v>74</v>
+      <c r="B2" t="s" s="5">
+        <v>89</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>27</v>
@@ -1379,11 +1424,11 @@
       </c>
     </row>
     <row ht="37.5" r="3" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="5">
         <v>47</v>
       </c>
-      <c r="B3" t="s">
-        <v>75</v>
+      <c r="B3" t="s" s="5">
+        <v>90</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>30</v>
@@ -1450,11 +1495,11 @@
       </c>
     </row>
     <row ht="37.5" r="4" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="5">
         <v>47</v>
       </c>
-      <c r="B4" t="s">
-        <v>76</v>
+      <c r="B4" t="s" s="5">
+        <v>91</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>31</v>
@@ -1491,11 +1536,11 @@
       </c>
     </row>
     <row customHeight="1" ht="42" r="5" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="5">
         <v>47</v>
       </c>
-      <c r="B5" t="s">
-        <v>77</v>
+      <c r="B5" t="s" s="5">
+        <v>92</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>32</v>
@@ -1533,11 +1578,11 @@
       </c>
     </row>
     <row ht="50" r="6" spans="1:31" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="5">
         <v>47</v>
       </c>
-      <c r="B6" t="s">
-        <v>78</v>
+      <c r="B6" t="s" s="5">
+        <v>93</v>
       </c>
       <c r="C6" s="16" t="s">
         <v>46</v>
